--- a/healthcare_forms/027_social_communication_questionnaire--healthcare_forms.xlsx
+++ b/healthcare_forms/027_social_communication_questionnaire--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>healthcare_provider_other</t>
+          <t>healthcare_provider_other_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>If other, please specify</t>
+          <t>Healthcare Provider Other 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,7 +934,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>social_isolation</t>
+          <t>social_isolation_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>If other, please specify</t>
+          <t>Social Support Services Other</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>If other, please specify</t>
+          <t>Social Worker Other</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1211,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>social_isolation_choices</t>
+          <t>social_isolation_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1359,7 +1359,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>social_isolation_choices</t>
+          <t>social_isolation_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
